--- a/output/pdf_financials_xlsx/RFX.xlsx
+++ b/output/pdf_financials_xlsx/RFX.xlsx
@@ -812,7 +812,7 @@
         <v>-0.049601</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-2.741404</v>
@@ -936,7 +936,7 @@
         <v>-0.049601</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-2.741404</v>
@@ -1011,7 +1011,7 @@
         <v>-0.049601</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-2.741404</v>
@@ -1119,7 +1119,7 @@
         <v>-0.049601</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.741404</v>
@@ -1169,7 +1169,7 @@
         <v>-0.049601</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.741404</v>
@@ -1229,7 +1229,7 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -2794,16 +2794,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.092167</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.092167</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.092167</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.092167</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0.005344</v>
@@ -5584,7 +5584,11 @@
           <t>Reserves (note 6 and 7)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -11515,10 +11519,10 @@
         <v>-0.049601</v>
       </c>
       <c r="H162" s="5" t="n">
-        <v>0.016168</v>
+        <v>-0.016168</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>0.012769</v>
+        <v>-0.012769</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RFX.xlsx
+++ b/output/pdf_financials_xlsx/RFX.xlsx
@@ -712,10 +712,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.012256</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.017767</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1119,10 +1119,10 @@
         <v>-0.049601</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.016168</v>
+        <v>-0.028424</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.741404</v>
+        <v>-2.759171</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.741404</v>
@@ -1169,10 +1169,10 @@
         <v>-0.049601</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.016168</v>
+        <v>-0.028424</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.741404</v>
+        <v>-2.759171</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.627463</v>
@@ -1287,22 +1287,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.200955</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.565863</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.523529</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.018407</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.119994</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.068782</v>
       </c>
     </row>
     <row r="35">
@@ -1337,22 +1337,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.200955</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.565863</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.523529</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.487256</v>
+        <v>0.505663</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.48447</v>
+        <v>0.604464</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.068782</v>
       </c>
     </row>
     <row r="37">
@@ -1652,7 +1652,7 @@
         <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.457344</v>
+        <v>0.388562</v>
       </c>
     </row>
     <row r="49">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
@@ -11330,7 +11330,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -11682,7 +11682,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">

--- a/output/pdf_financials_xlsx/RFX.xlsx
+++ b/output/pdf_financials_xlsx/RFX.xlsx
@@ -818,7 +818,7 @@
         <v>-2.741404</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-2.741404</v>
+        <v>-2.733896</v>
       </c>
     </row>
     <row r="17">
@@ -843,7 +843,7 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.007508</v>
       </c>
     </row>
     <row r="18">
@@ -1125,7 +1125,7 @@
         <v>-2.759171</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.741404</v>
+        <v>-2.733896</v>
       </c>
     </row>
     <row r="28">
@@ -1175,7 +1175,7 @@
         <v>-2.759171</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.627463</v>
+        <v>-2.619955</v>
       </c>
     </row>
     <row r="30">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-56.63244818785469</v>
+        <v>-56.47062043956882</v>
       </c>
     </row>
     <row r="31">
@@ -1235,7 +1235,7 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2746263939813365</v>
       </c>
     </row>
     <row r="32">
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.011817</v>
       </c>
     </row>
     <row r="111">
@@ -6178,7 +6178,11 @@
           <t>Accretion expense 15,16</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -7028,7 +7032,11 @@
           <t>Proceeds from share issuances 17(b)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -10358,7 +10366,11 @@
           <t>Income tax recovery 24</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
